--- a/booking_forms/044_forest_eco_retreat_booking_form--booking_forms.xlsx
+++ b/booking_forms/044_forest_eco_retreat_booking_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -968,8 +968,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -997,12 +997,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cottage'}</t>
+          <t>cottage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cottage'}</t>
+          <t>Cottage</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hut'}</t>
+          <t>hut</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hut'}</t>
+          <t>Hut</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cabin'}</t>
+          <t>cabin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cabin'}</t>
+          <t>Cabin</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'adult'}</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Adult'}</t>
+          <t>Adult</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'child'}</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Child'}</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'infant'}</t>
+          <t>infant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Infant'}</t>
+          <t>Infant</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unpaid'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unpaid'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
